--- a/public/files/templates/Template_Mahasiswa.xlsx
+++ b/public/files/templates/Template_Mahasiswa.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP Victus\Desktop\Template Excel Aplikasi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP Victus\Desktop\Asesmen-CPL\public\files\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EB2464E-83D3-413C-95CB-D0C45D068A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54182F56-CD6F-4E27-954A-FB16611B7AAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CACC8197-314A-458D-901D-784F30DA83A0}"/>
   </bookViews>
@@ -123,15 +123,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -139,21 +145,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -489,15 +515,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E21772E-3877-4860-B3FF-B1D11F685F69}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G52"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" zeroHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.77734375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="30.77734375" customWidth="1"/>
-    <col min="3" max="3" width="12.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="37.109375" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="40.77734375" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" style="1" customWidth="1"/>
     <col min="6" max="6" width="15.77734375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="0" hidden="1" customWidth="1"/>
     <col min="8" max="16384" width="8.88671875" hidden="1"/>
   </cols>
   <sheetData>
@@ -523,12 +550,417 @@
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D2" s="4"/>
+      <c r="A2" s="4"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="4"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="4"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="4"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="4"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="4"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="4"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="4"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="4"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="4"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="4"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="4"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="4"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="4"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="4"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="4"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="4"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="4"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="4"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="4"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="4"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="4"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="4"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="4"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="4"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="4"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="4"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="4"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="4"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="4"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="4"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="4"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="4"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="4"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="4"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="4"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="4"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="4"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="4"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="4"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="4"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="4"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="4"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="4"/>
+      <c r="B47" s="5"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="4"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="4"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="4"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="4"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="4"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="R8RMNabf6CHd2TttRifVpnmPBLWd9aAUyLFxbCGC+4lxfKLlw/KK6D6cnrN38/fezwemCI0K33VZXNMOzKDCnA==" saltValue="LJLrAi1UNOV5PHR6po+nNg==" spinCount="100000" sheet="1" objects="1" scenarios="1" insertRows="0" deleteRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="UJnXhY6P1WFLUhUGWSuLPSUedVHadxOD74VVdO+PiUW/TQbQkj2inodWTKaOK+JD+y8UTJjxDopCFnMmi8emQw==" saltValue="dfRIjAVqdrLB8XAAMarOLQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
-    <protectedRange sqref="A2:F1048576" name="Range1"/>
+    <protectedRange sqref="A2:F52" name="Range1"/>
   </protectedRanges>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
